--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/138.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/138.xlsx
@@ -426,13 +426,13 @@
         <v>-2.551802100904808</v>
       </c>
       <c r="E2">
-        <v>-19.96936123687505</v>
+        <v>-16.86067840702956</v>
       </c>
       <c r="F2">
-        <v>-0.7054104913472744</v>
+        <v>-0.7705731847210947</v>
       </c>
       <c r="G2">
-        <v>-11.47060866325971</v>
+        <v>-12.54751208890344</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.668306490324909</v>
       </c>
       <c r="E3">
-        <v>-20.97545591425813</v>
+        <v>-17.81541447316982</v>
       </c>
       <c r="F3">
-        <v>-0.7635295766950905</v>
+        <v>-0.3052701025271816</v>
       </c>
       <c r="G3">
-        <v>-12.07186705870998</v>
+        <v>-11.92744980553567</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.930146807504766</v>
       </c>
       <c r="E4">
-        <v>-21.5133756918386</v>
+        <v>-18.10041198749088</v>
       </c>
       <c r="F4">
-        <v>-0.8676222245308763</v>
+        <v>-0.5405653781901727</v>
       </c>
       <c r="G4">
-        <v>-11.95626981507696</v>
+        <v>-11.50559133540833</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.317296086241702</v>
       </c>
       <c r="E5">
-        <v>-22.36078447092265</v>
+        <v>-19.12846884635966</v>
       </c>
       <c r="F5">
-        <v>-0.3930720770195124</v>
+        <v>-0.4885704130512534</v>
       </c>
       <c r="G5">
-        <v>-12.10167915119591</v>
+        <v>-12.05013783147815</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.810634262489228</v>
       </c>
       <c r="E6">
-        <v>-23.26218084401813</v>
+        <v>-20.19034945825785</v>
       </c>
       <c r="F6">
-        <v>-0.2227995006392684</v>
+        <v>-0.2210425333779306</v>
       </c>
       <c r="G6">
-        <v>-11.80113806610072</v>
+        <v>-12.68354101970651</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.386669511673691</v>
       </c>
       <c r="E7">
-        <v>-24.05062232871226</v>
+        <v>-20.19855205062438</v>
       </c>
       <c r="F7">
-        <v>-1.345397206341339</v>
+        <v>-0.03251439617479115</v>
       </c>
       <c r="G7">
-        <v>-12.06787261948558</v>
+        <v>-12.2341183081862</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.016935111910223</v>
       </c>
       <c r="E8">
-        <v>-24.2651107743717</v>
+        <v>-21.52502960281607</v>
       </c>
       <c r="F8">
-        <v>0.5622252345435587</v>
+        <v>0.03952706011187625</v>
       </c>
       <c r="G8">
-        <v>-11.98428440991191</v>
+        <v>-12.27115563632803</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.65900197868832</v>
       </c>
       <c r="E9">
-        <v>-25.67809141203692</v>
+        <v>-21.35413326322203</v>
       </c>
       <c r="F9">
-        <v>0.2703557787389725</v>
+        <v>0.5454524513716743</v>
       </c>
       <c r="G9">
-        <v>-12.09405838773445</v>
+        <v>-12.5143243036612</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.280341821628843</v>
       </c>
       <c r="E10">
-        <v>-26.15069778832314</v>
+        <v>-22.71358731333286</v>
       </c>
       <c r="F10">
-        <v>-0.06185848305156083</v>
+        <v>0.7338795277516722</v>
       </c>
       <c r="G10">
-        <v>-13.34167970756337</v>
+        <v>-12.16201215332424</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.848413224437039</v>
       </c>
       <c r="E11">
-        <v>-28.09939077174967</v>
+        <v>-23.36198666536509</v>
       </c>
       <c r="F11">
-        <v>0.4462065812096683</v>
+        <v>1.025020848609198</v>
       </c>
       <c r="G11">
-        <v>-10.67952172321729</v>
+        <v>-12.21537707813889</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.327690336350611</v>
       </c>
       <c r="E12">
-        <v>-27.22717693802809</v>
+        <v>-23.38354598535227</v>
       </c>
       <c r="F12">
-        <v>1.581852730240637</v>
+        <v>1.300481174531728</v>
       </c>
       <c r="G12">
-        <v>-11.39384232930261</v>
+        <v>-12.26776427910417</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.699494895570883</v>
       </c>
       <c r="E13">
-        <v>-29.75682527478297</v>
+        <v>-25.90558771556573</v>
       </c>
       <c r="F13">
-        <v>1.007757671934856</v>
+        <v>1.685070622099066</v>
       </c>
       <c r="G13">
-        <v>-12.64832860203387</v>
+        <v>-12.27652854869654</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.955889131203755</v>
       </c>
       <c r="E14">
-        <v>-28.31413256329993</v>
+        <v>-25.58068199362439</v>
       </c>
       <c r="F14">
-        <v>1.18511113287423</v>
+        <v>2.110808392033066</v>
       </c>
       <c r="G14">
-        <v>-11.29645241844802</v>
+        <v>-11.81932190217782</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.090892527903963</v>
       </c>
       <c r="E15">
-        <v>-30.61292880177554</v>
+        <v>-27.82705432215235</v>
       </c>
       <c r="F15">
-        <v>1.366853284313636</v>
+        <v>2.276399035852688</v>
       </c>
       <c r="G15">
-        <v>-11.97621981986996</v>
+        <v>-11.93621538050033</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.117219430665971</v>
       </c>
       <c r="E16">
-        <v>-30.77457386314353</v>
+        <v>-27.21396557280382</v>
       </c>
       <c r="F16">
-        <v>2.009684612968914</v>
+        <v>2.537505411419509</v>
       </c>
       <c r="G16">
-        <v>-10.59019379166005</v>
+        <v>-10.89316286922497</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.061109727890219</v>
       </c>
       <c r="E17">
-        <v>-31.63346834814639</v>
+        <v>-28.54069647088632</v>
       </c>
       <c r="F17">
-        <v>2.535305267597673</v>
+        <v>2.929732406440658</v>
       </c>
       <c r="G17">
-        <v>-10.44841208515046</v>
+        <v>-10.91489731794599</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.947422517390757</v>
       </c>
       <c r="E18">
-        <v>-32.52174680327241</v>
+        <v>-29.25500313343225</v>
       </c>
       <c r="F18">
-        <v>2.597467614238554</v>
+        <v>3.68182539552519</v>
       </c>
       <c r="G18">
-        <v>-10.07495290362548</v>
+        <v>-10.07008255959076</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.80584879479481</v>
       </c>
       <c r="E19">
-        <v>-33.99733917826507</v>
+        <v>-30.34951967992094</v>
       </c>
       <c r="F19">
-        <v>3.177533544783713</v>
+        <v>3.664785878049605</v>
       </c>
       <c r="G19">
-        <v>-9.92859717259226</v>
+        <v>-10.14047084451176</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.669774847422731</v>
       </c>
       <c r="E20">
-        <v>-35.3808714710316</v>
+        <v>-31.31642465524295</v>
       </c>
       <c r="F20">
-        <v>3.10970682184249</v>
+        <v>4.494298084599779</v>
       </c>
       <c r="G20">
-        <v>-9.183447589002776</v>
+        <v>-9.51593243954253</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.558746925813715</v>
       </c>
       <c r="E21">
-        <v>-35.80820161406019</v>
+        <v>-32.43030762613932</v>
       </c>
       <c r="F21">
-        <v>3.477929386265314</v>
+        <v>4.824987322001759</v>
       </c>
       <c r="G21">
-        <v>-9.308993074900231</v>
+        <v>-9.394594168553654</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.481340695109818</v>
       </c>
       <c r="E22">
-        <v>-35.81093858032325</v>
+        <v>-33.33490197195492</v>
       </c>
       <c r="F22">
-        <v>3.667710014981487</v>
+        <v>5.123232721705692</v>
       </c>
       <c r="G22">
-        <v>-9.531948052236714</v>
+        <v>-9.290502476333671</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.44684712449143</v>
       </c>
       <c r="E23">
-        <v>-37.19154908892276</v>
+        <v>-33.21510259129024</v>
       </c>
       <c r="F23">
-        <v>4.107168862575458</v>
+        <v>5.375909630581626</v>
       </c>
       <c r="G23">
-        <v>-8.058998588237989</v>
+        <v>-8.714625739798199</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.452698602523616</v>
       </c>
       <c r="E24">
-        <v>-37.68636060955717</v>
+        <v>-34.97666225544832</v>
       </c>
       <c r="F24">
-        <v>5.256333139252711</v>
+        <v>5.642365602835726</v>
       </c>
       <c r="G24">
-        <v>-8.354310351917176</v>
+        <v>-7.531228736910664</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.484572827460642</v>
       </c>
       <c r="E25">
-        <v>-35.73908802440372</v>
+        <v>-35.22866042918795</v>
       </c>
       <c r="F25">
-        <v>4.997899076927322</v>
+        <v>5.469670880169696</v>
       </c>
       <c r="G25">
-        <v>-7.891694242605675</v>
+        <v>-8.066799493076234</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.533638540639368</v>
       </c>
       <c r="E26">
-        <v>-38.07613741578666</v>
+        <v>-34.73355818376081</v>
       </c>
       <c r="F26">
-        <v>4.641538733712586</v>
+        <v>6.305738786345626</v>
       </c>
       <c r="G26">
-        <v>-6.981395483043841</v>
+        <v>-8.169661524593803</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.587506944992124</v>
       </c>
       <c r="E27">
-        <v>-38.23283184925545</v>
+        <v>-35.85620858376388</v>
       </c>
       <c r="F27">
-        <v>4.242192749231777</v>
+        <v>6.292536266679807</v>
       </c>
       <c r="G27">
-        <v>-8.914010914966111</v>
+        <v>-8.356106544195862</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.624253643484487</v>
       </c>
       <c r="E28">
-        <v>-39.80066912437823</v>
+        <v>-35.97839398433468</v>
       </c>
       <c r="F28">
-        <v>5.13293456072728</v>
+        <v>5.666732858356476</v>
       </c>
       <c r="G28">
-        <v>-7.587738303585311</v>
+        <v>-8.668517379574547</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.631271521017508</v>
       </c>
       <c r="E29">
-        <v>-38.75071030558797</v>
+        <v>-35.76439561761156</v>
       </c>
       <c r="F29">
-        <v>4.6258014097942</v>
+        <v>5.694952022300244</v>
       </c>
       <c r="G29">
-        <v>-8.507536257341911</v>
+        <v>-7.690545509466466</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.601384432730691</v>
       </c>
       <c r="E30">
-        <v>-38.49297239379742</v>
+        <v>-36.07830571257041</v>
       </c>
       <c r="F30">
-        <v>4.449610976688357</v>
+        <v>5.577575674793166</v>
       </c>
       <c r="G30">
-        <v>-8.158888287038573</v>
+        <v>-8.417769720693366</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.521452836219752</v>
       </c>
       <c r="E31">
-        <v>-39.23098558658548</v>
+        <v>-35.17242179463845</v>
       </c>
       <c r="F31">
-        <v>4.802859971938179</v>
+        <v>5.388393127341814</v>
       </c>
       <c r="G31">
-        <v>-7.270994937557674</v>
+        <v>-7.701065504796357</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.386543008037092</v>
       </c>
       <c r="E32">
-        <v>-37.20923969256086</v>
+        <v>-35.37323163879957</v>
       </c>
       <c r="F32">
-        <v>3.371338382342685</v>
+        <v>4.991376511997679</v>
       </c>
       <c r="G32">
-        <v>-9.455365775773293</v>
+        <v>-7.873199727922229</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.201775191346104</v>
       </c>
       <c r="E33">
-        <v>-37.43320576646357</v>
+        <v>-35.40172682169922</v>
       </c>
       <c r="F33">
-        <v>3.805697800205023</v>
+        <v>4.640488363845836</v>
       </c>
       <c r="G33">
-        <v>-7.155096152924382</v>
+        <v>-7.854462413991809</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.96464448923946</v>
       </c>
       <c r="E34">
-        <v>-37.06933669247835</v>
+        <v>-35.53828025684826</v>
       </c>
       <c r="F34">
-        <v>4.043099614173333</v>
+        <v>4.854134257436662</v>
       </c>
       <c r="G34">
-        <v>-6.164062727626961</v>
+        <v>-8.174879097659142</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.674809937966778</v>
       </c>
       <c r="E35">
-        <v>-36.78124711232596</v>
+        <v>-34.36055204486097</v>
       </c>
       <c r="F35">
-        <v>3.181347348306202</v>
+        <v>4.64210202354649</v>
       </c>
       <c r="G35">
-        <v>-7.080896180900351</v>
+        <v>-7.547342252527015</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.340986883430015</v>
       </c>
       <c r="E36">
-        <v>-37.97051502197929</v>
+        <v>-34.44150021018753</v>
       </c>
       <c r="F36">
-        <v>3.010617513119612</v>
+        <v>4.141377122841466</v>
       </c>
       <c r="G36">
-        <v>-7.473403354962096</v>
+        <v>-7.419251290653224</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.964904753583497</v>
       </c>
       <c r="E37">
-        <v>-35.76328048037085</v>
+        <v>-33.87665931679953</v>
       </c>
       <c r="F37">
-        <v>3.203835866557403</v>
+        <v>4.108106574475427</v>
       </c>
       <c r="G37">
-        <v>-7.799829972678173</v>
+        <v>-6.274053397250563</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.546267304382564</v>
       </c>
       <c r="E38">
-        <v>-37.13826338762521</v>
+        <v>-32.92756331163839</v>
       </c>
       <c r="F38">
-        <v>2.899952598310016</v>
+        <v>3.881415551025314</v>
       </c>
       <c r="G38">
-        <v>-6.549640985543891</v>
+        <v>-6.997399347387366</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.093494034765715</v>
       </c>
       <c r="E39">
-        <v>-38.37811325800362</v>
+        <v>-32.86814954703105</v>
       </c>
       <c r="F39">
-        <v>2.838837308066274</v>
+        <v>3.202343148497558</v>
       </c>
       <c r="G39">
-        <v>-6.882698894521395</v>
+        <v>-6.702165906045911</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.610932799748519</v>
       </c>
       <c r="E40">
-        <v>-36.24772350893282</v>
+        <v>-31.70734359458677</v>
       </c>
       <c r="F40">
-        <v>3.467728870067242</v>
+        <v>3.23029723487243</v>
       </c>
       <c r="G40">
-        <v>-6.598999722783478</v>
+        <v>-6.145080003704976</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.099629467614879</v>
       </c>
       <c r="E41">
-        <v>-34.67902859567147</v>
+        <v>-32.18078684295494</v>
       </c>
       <c r="F41">
-        <v>2.387706763766857</v>
+        <v>3.078656298115953</v>
       </c>
       <c r="G41">
-        <v>-5.160664815946027</v>
+        <v>-5.781734846725967</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.567502837140475</v>
       </c>
       <c r="E42">
-        <v>-34.05961242886956</v>
+        <v>-31.87679254003412</v>
       </c>
       <c r="F42">
-        <v>2.387222997203622</v>
+        <v>2.964745839822187</v>
       </c>
       <c r="G42">
-        <v>-5.939804988739512</v>
+        <v>-4.969801111123508</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.022171833720091</v>
       </c>
       <c r="E43">
-        <v>-33.87831021830115</v>
+        <v>-31.228663146738</v>
       </c>
       <c r="F43">
-        <v>2.388445667490154</v>
+        <v>2.779095450976373</v>
       </c>
       <c r="G43">
-        <v>-5.658431990432278</v>
+        <v>-5.083514702534038</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.467690747226726</v>
       </c>
       <c r="E44">
-        <v>-33.91033978403823</v>
+        <v>-30.86612102377106</v>
       </c>
       <c r="F44">
-        <v>3.202222206856749</v>
+        <v>2.456199494099931</v>
       </c>
       <c r="G44">
-        <v>-5.406249727398281</v>
+        <v>-4.808206463911961</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.911893054382262</v>
       </c>
       <c r="E45">
-        <v>-34.69802330766557</v>
+        <v>-31.00411562324982</v>
       </c>
       <c r="F45">
-        <v>2.128106360138326</v>
+        <v>3.021343214251061</v>
       </c>
       <c r="G45">
-        <v>-5.026939867244614</v>
+        <v>-5.218278727582716</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.365022282984964</v>
       </c>
       <c r="E46">
-        <v>-34.48614723192944</v>
+        <v>-31.66699099335474</v>
       </c>
       <c r="F46">
-        <v>2.632903514995511</v>
+        <v>2.295020735067621</v>
       </c>
       <c r="G46">
-        <v>-5.66514421477603</v>
+        <v>-4.343303342338644</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.8328990067653936</v>
       </c>
       <c r="E47">
-        <v>-33.65638752437026</v>
+        <v>-29.45652940654691</v>
       </c>
       <c r="F47">
-        <v>2.451547382765809</v>
+        <v>2.470220440759716</v>
       </c>
       <c r="G47">
-        <v>-4.193822550029862</v>
+        <v>-4.007015942301933</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3212905721404052</v>
       </c>
       <c r="E48">
-        <v>-33.44889516318749</v>
+        <v>-29.10857543835844</v>
       </c>
       <c r="F48">
-        <v>1.455906093584194</v>
+        <v>2.258720018742141</v>
       </c>
       <c r="G48">
-        <v>-5.646827230724779</v>
+        <v>-4.159548695037727</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.1592446809749285</v>
       </c>
       <c r="E49">
-        <v>-32.30004422954173</v>
+        <v>-28.36674959757418</v>
       </c>
       <c r="F49">
-        <v>1.634997469334642</v>
+        <v>2.396631594164619</v>
       </c>
       <c r="G49">
-        <v>-4.792421902114089</v>
+        <v>-4.183732022185209</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.601364021127281</v>
       </c>
       <c r="E50">
-        <v>-31.7882834534907</v>
+        <v>-29.0958977607894</v>
       </c>
       <c r="F50">
-        <v>1.734848876068094</v>
+        <v>2.14819923986063</v>
       </c>
       <c r="G50">
-        <v>-5.017509857781512</v>
+        <v>-4.235119307972091</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.00019758315661</v>
       </c>
       <c r="E51">
-        <v>-32.29400338366977</v>
+        <v>-27.37722000356018</v>
       </c>
       <c r="F51">
-        <v>1.876991752184072</v>
+        <v>2.077483171418443</v>
       </c>
       <c r="G51">
-        <v>-4.77710988508721</v>
+        <v>-4.317488299821716</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.345782053335009</v>
       </c>
       <c r="E52">
-        <v>-32.21620335252742</v>
+        <v>-28.01298113353095</v>
       </c>
       <c r="F52">
-        <v>1.512937532532135</v>
+        <v>1.982853792792238</v>
       </c>
       <c r="G52">
-        <v>-4.248671683144561</v>
+        <v>-3.902533943765579</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.631719802387548</v>
       </c>
       <c r="E53">
-        <v>-29.46836190561135</v>
+        <v>-27.22004587418336</v>
       </c>
       <c r="F53">
-        <v>1.5380784832071</v>
+        <v>2.003107375790686</v>
       </c>
       <c r="G53">
-        <v>-5.104379773306216</v>
+        <v>-3.655090182164453</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.854574548252439</v>
       </c>
       <c r="E54">
-        <v>-29.57874595620264</v>
+        <v>-27.01126394088423</v>
       </c>
       <c r="F54">
-        <v>1.257051528337756</v>
+        <v>1.614230298546458</v>
       </c>
       <c r="G54">
-        <v>-3.893440720354732</v>
+        <v>-3.599392557057642</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.007424484684006</v>
       </c>
       <c r="E55">
-        <v>-29.69286789698628</v>
+        <v>-26.10909922369365</v>
       </c>
       <c r="F55">
-        <v>1.720148668138014</v>
+        <v>1.45163503125536</v>
       </c>
       <c r="G55">
-        <v>-4.698539526617656</v>
+        <v>-4.2190762824597</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.088216918900959</v>
       </c>
       <c r="E56">
-        <v>-27.62921610069415</v>
+        <v>-25.27009654433106</v>
       </c>
       <c r="F56">
-        <v>1.15446485244026</v>
+        <v>1.652674829710383</v>
       </c>
       <c r="G56">
-        <v>-5.264340094403727</v>
+        <v>-4.137320815588988</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.097543851750794</v>
       </c>
       <c r="E57">
-        <v>-28.78688222537685</v>
+        <v>-25.25503284685591</v>
       </c>
       <c r="F57">
-        <v>1.728922735668466</v>
+        <v>1.159120277243993</v>
       </c>
       <c r="G57">
-        <v>-4.136454048384739</v>
+        <v>-4.3511016364323</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.036535879941798</v>
       </c>
       <c r="E58">
-        <v>-26.86709766937678</v>
+        <v>-24.93137724152335</v>
       </c>
       <c r="F58">
-        <v>1.823472591024002</v>
+        <v>1.354653089205205</v>
       </c>
       <c r="G58">
-        <v>-4.934866737749822</v>
+        <v>-4.700434927190804</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.910085262523036</v>
       </c>
       <c r="E59">
-        <v>-27.05420814598296</v>
+        <v>-24.3809479914325</v>
       </c>
       <c r="F59">
-        <v>1.08392605462227</v>
+        <v>0.8896970929530649</v>
       </c>
       <c r="G59">
-        <v>-5.024256021804949</v>
+        <v>-4.682334634940616</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.724675524485685</v>
       </c>
       <c r="E60">
-        <v>-26.02247984830303</v>
+        <v>-24.54964728223571</v>
       </c>
       <c r="F60">
-        <v>0.8996043670905469</v>
+        <v>1.489211433381151</v>
       </c>
       <c r="G60">
-        <v>-4.504336679463103</v>
+        <v>-4.554940741872652</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.489008925330249</v>
       </c>
       <c r="E61">
-        <v>-27.58967752888178</v>
+        <v>-23.76140099847385</v>
       </c>
       <c r="F61">
-        <v>1.887515331669237</v>
+        <v>0.9608919577540712</v>
       </c>
       <c r="G61">
-        <v>-5.966142180174662</v>
+        <v>-4.960381544638771</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.214995690881226</v>
       </c>
       <c r="E62">
-        <v>-27.5208629704407</v>
+        <v>-23.75517948790925</v>
       </c>
       <c r="F62">
-        <v>0.9373596965753428</v>
+        <v>1.161930099474289</v>
       </c>
       <c r="G62">
-        <v>-5.861117146763357</v>
+        <v>-5.511606325372657</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.9157192313817204</v>
       </c>
       <c r="E63">
-        <v>-25.96762423312469</v>
+        <v>-22.27198465958649</v>
       </c>
       <c r="F63">
-        <v>1.388410717604091</v>
+        <v>0.450422142922515</v>
       </c>
       <c r="G63">
-        <v>-5.819632415210568</v>
+        <v>-5.647192734967534</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.6061441278165908</v>
       </c>
       <c r="E64">
-        <v>-25.46499844538262</v>
+        <v>-22.3922408934969</v>
       </c>
       <c r="F64">
-        <v>1.211734861200206</v>
+        <v>0.2723388903012745</v>
       </c>
       <c r="G64">
-        <v>-5.671441330729795</v>
+        <v>-6.231965583697226</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.3020764914197275</v>
       </c>
       <c r="E65">
-        <v>-23.41901441006631</v>
+        <v>-22.38981126487187</v>
       </c>
       <c r="F65">
-        <v>1.193981291023407</v>
+        <v>0.8028725919960374</v>
       </c>
       <c r="G65">
-        <v>-7.713467846976441</v>
+        <v>-5.895675572915924</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.01758813506052773</v>
       </c>
       <c r="E66">
-        <v>-25.32346530985511</v>
+        <v>-22.53891985785587</v>
       </c>
       <c r="F66">
-        <v>0.04474991658652714</v>
+        <v>0.3727527585012278</v>
       </c>
       <c r="G66">
-        <v>-6.679167856942795</v>
+        <v>-5.946676468503322</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.2324222377688281</v>
       </c>
       <c r="E67">
-        <v>-26.90522414933871</v>
+        <v>-21.42989614420955</v>
       </c>
       <c r="F67">
-        <v>0.5719163047889101</v>
+        <v>0.2594718594335898</v>
       </c>
       <c r="G67">
-        <v>-5.983895243394233</v>
+        <v>-5.750888899381963</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.4330213686302428</v>
       </c>
       <c r="E68">
-        <v>-26.70064111268898</v>
+        <v>-22.42011309469782</v>
       </c>
       <c r="F68">
-        <v>0.3506684835425929</v>
+        <v>0.3602245299012881</v>
       </c>
       <c r="G68">
-        <v>-6.859113427885277</v>
+        <v>-6.132081106385823</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5740577949619491</v>
       </c>
       <c r="E69">
-        <v>-24.06658311983357</v>
+        <v>-21.25323514729664</v>
       </c>
       <c r="F69">
-        <v>0.2272375986884526</v>
+        <v>-0.5164342073792203</v>
       </c>
       <c r="G69">
-        <v>-6.441094057679174</v>
+        <v>-5.91649103954087</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6455729451100405</v>
       </c>
       <c r="E70">
-        <v>-25.17615090416344</v>
+        <v>-21.40953710229524</v>
       </c>
       <c r="F70">
-        <v>-0.06236792900428253</v>
+        <v>-0.4282578108208241</v>
       </c>
       <c r="G70">
-        <v>-6.116688156276619</v>
+        <v>-5.896529286397218</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.6385746266734021</v>
       </c>
       <c r="E71">
-        <v>-24.22989569554848</v>
+        <v>-21.44852745021273</v>
       </c>
       <c r="F71">
-        <v>0.1436669248896217</v>
+        <v>-0.5646576157331935</v>
       </c>
       <c r="G71">
-        <v>-5.878400275956527</v>
+        <v>-6.141328363727546</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5507833747131655</v>
       </c>
       <c r="E72">
-        <v>-24.88115661018352</v>
+        <v>-21.10749065548576</v>
       </c>
       <c r="F72">
-        <v>-0.3093746630080531</v>
+        <v>-0.5343725034868436</v>
       </c>
       <c r="G72">
-        <v>-6.405872502400465</v>
+        <v>-5.684432395815175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3781953715301248</v>
       </c>
       <c r="E73">
-        <v>-26.49808068995444</v>
+        <v>-21.31748532649174</v>
       </c>
       <c r="F73">
-        <v>-0.1503977045323832</v>
+        <v>-0.3799118040912366</v>
       </c>
       <c r="G73">
-        <v>-4.631795841145845</v>
+        <v>-5.562912678077216</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1195784675929995</v>
       </c>
       <c r="E74">
-        <v>-26.16681640147479</v>
+        <v>-22.64628452381401</v>
       </c>
       <c r="F74">
-        <v>-0.8254425847477284</v>
+        <v>-0.6891794604568209</v>
       </c>
       <c r="G74">
-        <v>-5.867683169410007</v>
+        <v>-4.964770206296433</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2165949313031574</v>
       </c>
       <c r="E75">
-        <v>-25.42790196182925</v>
+        <v>-21.52974765088108</v>
       </c>
       <c r="F75">
-        <v>0.1461992440399798</v>
+        <v>-0.9167203888622059</v>
       </c>
       <c r="G75">
-        <v>-4.843749140775377</v>
+        <v>-4.850205512149199</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6243825900264993</v>
       </c>
       <c r="E76">
-        <v>-25.5367742434983</v>
+        <v>-22.08406015356064</v>
       </c>
       <c r="F76">
-        <v>-1.256693139747359</v>
+        <v>-1.082784858836228</v>
       </c>
       <c r="G76">
-        <v>-4.343705397005675</v>
+        <v>-4.826382467755291</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.094755594058427</v>
       </c>
       <c r="E77">
-        <v>-23.89633052799488</v>
+        <v>-22.54021981300054</v>
       </c>
       <c r="F77">
-        <v>-0.7814397083110186</v>
+        <v>-1.176457473112199</v>
       </c>
       <c r="G77">
-        <v>-4.686665860217272</v>
+        <v>-4.018427506909689</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.611704866548826</v>
       </c>
       <c r="E78">
-        <v>-25.94466528092104</v>
+        <v>-23.23019696360563</v>
       </c>
       <c r="F78">
-        <v>-0.7556219814679663</v>
+        <v>-0.9334393281529083</v>
       </c>
       <c r="G78">
-        <v>-3.812129080064508</v>
+        <v>-3.937836432126613</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.16196233336663</v>
       </c>
       <c r="E79">
-        <v>-25.72973659486116</v>
+        <v>-23.17587711268819</v>
       </c>
       <c r="F79">
-        <v>-1.105920332029016</v>
+        <v>-1.435270927708071</v>
       </c>
       <c r="G79">
-        <v>-3.067267983752341</v>
+        <v>-3.450050134212189</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.731327234507554</v>
       </c>
       <c r="E80">
-        <v>-26.27984189446868</v>
+        <v>-23.11660248066024</v>
       </c>
       <c r="F80">
-        <v>-0.5484191295361148</v>
+        <v>-1.496901462476354</v>
       </c>
       <c r="G80">
-        <v>-3.601530756877764</v>
+        <v>-2.995984213436584</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.300193062284738</v>
       </c>
       <c r="E81">
-        <v>-29.46488566773246</v>
+        <v>-23.92598445685415</v>
       </c>
       <c r="F81">
-        <v>-0.7993233321700571</v>
+        <v>-1.510494143188891</v>
       </c>
       <c r="G81">
-        <v>-3.039252083545104</v>
+        <v>-2.789928585838377</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.850820278645105</v>
       </c>
       <c r="E82">
-        <v>-26.87325272856018</v>
+        <v>-25.25011959785864</v>
       </c>
       <c r="F82">
-        <v>-1.556823075292662</v>
+        <v>-1.158812419065167</v>
       </c>
       <c r="G82">
-        <v>-3.226395477325287</v>
+        <v>-2.448667717355595</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.367779604026111</v>
       </c>
       <c r="E83">
-        <v>-27.44490904173223</v>
+        <v>-26.21548788499046</v>
       </c>
       <c r="F83">
-        <v>-1.708107814065936</v>
+        <v>-1.339672359220591</v>
       </c>
       <c r="G83">
-        <v>-2.246128762721617</v>
+        <v>-1.774145301817202</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.832550483541255</v>
       </c>
       <c r="E84">
-        <v>-30.24622100784981</v>
+        <v>-26.67224560686113</v>
       </c>
       <c r="F84">
-        <v>-1.479661480089291</v>
+        <v>-1.521398771679344</v>
       </c>
       <c r="G84">
-        <v>-2.258952740153166</v>
+        <v>-1.889514105298498</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.22852514753755</v>
       </c>
       <c r="E85">
-        <v>-31.48005287501855</v>
+        <v>-28.27746801372435</v>
       </c>
       <c r="F85">
-        <v>-0.9373583343355527</v>
+        <v>-1.227247163680045</v>
       </c>
       <c r="G85">
-        <v>-2.453803051966315</v>
+        <v>-1.738365047195994</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.543275366079159</v>
       </c>
       <c r="E86">
-        <v>-30.36416182644663</v>
+        <v>-28.56065472790778</v>
       </c>
       <c r="F86">
-        <v>-1.248686968799302</v>
+        <v>-1.311952700820711</v>
       </c>
       <c r="G86">
-        <v>-1.222494969714965</v>
+        <v>-1.069988324425082</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.763930876269803</v>
       </c>
       <c r="E87">
-        <v>-31.7832995999009</v>
+        <v>-30.65441522969926</v>
       </c>
       <c r="F87">
-        <v>-1.069651922032245</v>
+        <v>-1.448358304304901</v>
       </c>
       <c r="G87">
-        <v>-1.902907225050909</v>
+        <v>-1.376876129621267</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.878811098245951</v>
       </c>
       <c r="E88">
-        <v>-31.65164280090384</v>
+        <v>-31.63185067233537</v>
       </c>
       <c r="F88">
-        <v>-1.935416799598537</v>
+        <v>-1.526335013032626</v>
       </c>
       <c r="G88">
-        <v>-2.730489763732501</v>
+        <v>-1.657627770715816</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.879959849116124</v>
       </c>
       <c r="E89">
-        <v>-33.01681789961462</v>
+        <v>-32.33654057405866</v>
       </c>
       <c r="F89">
-        <v>-1.408916418788005</v>
+        <v>-1.207964427277678</v>
       </c>
       <c r="G89">
-        <v>-2.223235143402145</v>
+        <v>-1.586025489559943</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.762203519082473</v>
       </c>
       <c r="E90">
-        <v>-36.28170923720389</v>
+        <v>-34.49118715387213</v>
       </c>
       <c r="F90">
-        <v>-1.372038330382774</v>
+        <v>-1.28335662970867</v>
       </c>
       <c r="G90">
-        <v>-1.630875470890678</v>
+        <v>-1.407202538791638</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.522843209001345</v>
       </c>
       <c r="E91">
-        <v>-35.67560826590937</v>
+        <v>-35.55977935527123</v>
       </c>
       <c r="F91">
-        <v>-1.542028433478663</v>
+        <v>-1.346167588025942</v>
       </c>
       <c r="G91">
-        <v>-2.668920574040276</v>
+        <v>-1.952568808663066</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.160628176867679</v>
       </c>
       <c r="E92">
-        <v>-37.75179237737418</v>
+        <v>-36.40121581647017</v>
       </c>
       <c r="F92">
-        <v>-1.368921183846039</v>
+        <v>-1.084682648556042</v>
       </c>
       <c r="G92">
-        <v>-2.100449214537496</v>
+        <v>-1.997664199985366</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.681510776182328</v>
       </c>
       <c r="E93">
-        <v>-39.97432527289762</v>
+        <v>-39.34345870247316</v>
       </c>
       <c r="F93">
-        <v>-0.7960670199096522</v>
+        <v>-1.027247794682938</v>
       </c>
       <c r="G93">
-        <v>-3.852940239512791</v>
+        <v>-2.421064314793754</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.094595865156411</v>
       </c>
       <c r="E94">
-        <v>-40.73186063551804</v>
+        <v>-41.10982986195105</v>
       </c>
       <c r="F94">
-        <v>-1.160619088370673</v>
+        <v>-0.7171352035664985</v>
       </c>
       <c r="G94">
-        <v>-2.612136879183562</v>
+        <v>-2.384226708613146</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.409438912632058</v>
       </c>
       <c r="E95">
-        <v>-41.50953491985255</v>
+        <v>-42.87903974136946</v>
       </c>
       <c r="F95">
-        <v>-2.396485267629339</v>
+        <v>-0.6466676453451502</v>
       </c>
       <c r="G95">
-        <v>-3.869246950228885</v>
+        <v>-3.799221558806044</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.639398518850783</v>
       </c>
       <c r="E96">
-        <v>-45.66954816652832</v>
+        <v>-44.44600899532534</v>
       </c>
       <c r="F96">
-        <v>-2.307889717165126</v>
+        <v>-0.54245239913375</v>
       </c>
       <c r="G96">
-        <v>-3.768699343791339</v>
+        <v>-3.205666165271848</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.813075378310359</v>
       </c>
       <c r="E97">
-        <v>-47.38680137227313</v>
+        <v>-45.55674279373466</v>
       </c>
       <c r="F97">
-        <v>-1.525379905417199</v>
+        <v>-0.4275636389372782</v>
       </c>
       <c r="G97">
-        <v>-4.202936659397438</v>
+        <v>-3.99765120145361</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.9315343105867283</v>
       </c>
       <c r="E98">
-        <v>-48.24585264100349</v>
+        <v>-48.09917990646152</v>
       </c>
       <c r="F98">
-        <v>-0.8566828046095061</v>
+        <v>-0.2172320433250529</v>
       </c>
       <c r="G98">
-        <v>-4.838767840095533</v>
+        <v>-4.721433145937128</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.04398267204724007</v>
       </c>
       <c r="E99">
-        <v>-50.79292681417453</v>
+        <v>-50.52838490393108</v>
       </c>
       <c r="F99">
-        <v>-0.3490344091518851</v>
+        <v>-0.07004855156303955</v>
       </c>
       <c r="G99">
-        <v>-5.678430294000205</v>
+        <v>-4.712141505937356</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.864778017396227</v>
       </c>
       <c r="E100">
-        <v>-51.99036512880662</v>
+        <v>-51.893817501744</v>
       </c>
       <c r="F100">
-        <v>-0.8806847501056217</v>
+        <v>-0.08225454524329026</v>
       </c>
       <c r="G100">
-        <v>-5.244686409121826</v>
+        <v>-5.619283875288533</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.715428718773731</v>
       </c>
       <c r="E101">
-        <v>-52.58120097187673</v>
+        <v>-54.68032534609422</v>
       </c>
       <c r="F101">
-        <v>-0.008654929871956986</v>
+        <v>0.5292288757878459</v>
       </c>
       <c r="G101">
-        <v>-6.176774443041091</v>
+        <v>-5.637640020508651</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.591830189963049</v>
       </c>
       <c r="E102">
-        <v>-55.86207023258404</v>
+        <v>-56.53850064615037</v>
       </c>
       <c r="F102">
-        <v>-0.8313248216750077</v>
+        <v>0.8730154301954884</v>
       </c>
       <c r="G102">
-        <v>-6.329147940356827</v>
+        <v>-6.170782784204486</v>
       </c>
     </row>
   </sheetData>
